--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ギルド別成績" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="頻出対戦ペア" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="偏った対戦結果(要確認)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="戦闘形式別集計" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N人巴_頻出組み合わせ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月別参加数" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新規参入_離脱" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拠点別入札状況" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ギルド別成績" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="頻出対戦ペア" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="偏った対戦結果(要確認)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="戦闘形式別集計" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="N人巴_頻出組み合わせ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="月別参加数" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="新規参入_離脱" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="拠点別入札状況" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-08-31</t>
+          <t>2025-08-01 〜 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2086</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.3673</v>
+        <v>0.3716</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>31</v>
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4818</v>
+        <v>0.4775</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>7</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5909</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>11</v>
@@ -1296,48 +1296,48 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
         <v>96</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.1458</v>
+        <v>0.3646</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
         <v>96</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.125</v>
+        <v>0.1458</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
@@ -1346,26 +1346,26 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.3684</v>
+        <v>0.125</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.2821</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>11</v>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.1818</v>
+        <v>0.1795</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>21</v>
@@ -1746,76 +1746,76 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.15</v>
+        <v>0.1639</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>SЕRЕNIТY</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
         <v>60</v>
       </c>
       <c r="C48" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="D48" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="F48" s="5" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
         <v>60</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.35</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C86" s="5" t="n">
         <v>0</v>
@@ -6089,54 +6089,54 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
@@ -6146,81 +6146,81 @@
         <v>6</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
+          <t>東京熱株式會社</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
           <t>雪狼族</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
@@ -6230,49 +6230,49 @@
         <v>3</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -6467,190 +6467,190 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D65" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="D65" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -6661,38 +6661,38 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -6703,182 +6703,182 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>6</v>
@@ -7202,82 +7202,82 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>6</v>
@@ -7286,40 +7286,40 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -7328,82 +7328,82 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>4</v>
@@ -7664,40 +7664,40 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>一SUN一</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
           <t>當惡魔遇到殺手貓</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0</v>
@@ -7706,82 +7706,82 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>4</v>
@@ -7790,19 +7790,19 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>4</v>
@@ -7811,33 +7811,33 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
@@ -7847,60 +7847,60 @@
         <v>3</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
@@ -7916,12 +7916,12 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
@@ -7931,34 +7931,34 @@
         <v>2</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -7970,52 +7970,52 @@
         <v>11</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
           <t>義勇</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
@@ -8036,91 +8036,91 @@
         <v>1</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -8131,14 +8131,14 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E144" s="5" t="n">
         <v>3</v>
@@ -8147,40 +8147,40 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E146" s="5" t="n">
         <v>4</v>
@@ -8924,19 +8924,19 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E182" s="5" t="n">
         <v>3</v>
@@ -8945,12 +8945,12 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
@@ -8960,46 +8960,46 @@
         <v>3</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E185" s="5" t="n">
         <v>1</v>
@@ -9008,19 +9008,19 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E186" s="5" t="n">
         <v>2</v>
@@ -9029,19 +9029,19 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" s="5" t="n">
         <v>1</v>
@@ -9050,40 +9050,40 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>1</v>
@@ -9092,19 +9092,19 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
+          <t>ひよこりあ</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
           <t>月下の集い</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" s="5" t="n">
         <v>1</v>
@@ -9113,33 +9113,33 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
@@ -9149,97 +9149,97 @@
         <v>1</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
+          <t>Oops</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
           <t>・殺戮・</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
-        <is>
-          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E196" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -9254,25 +9254,25 @@
         <v>0</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E198" s="5" t="n">
         <v>0</v>
@@ -9281,40 +9281,40 @@
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E200" s="5" t="n">
         <v>0</v>
@@ -9323,22 +9323,22 @@
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9352,7 +9352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -10570,26 +10570,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -10599,7 +10599,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -10628,7 +10628,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -10657,26 +10657,26 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
@@ -10686,117 +10686,117 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.9</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.889</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
@@ -10831,55 +10831,55 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E51" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
@@ -10889,12 +10889,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
@@ -10918,26 +10918,26 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
@@ -10947,70 +10947,70 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
@@ -11034,12 +11034,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
@@ -11063,26 +11063,26 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
@@ -11092,12 +11092,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
@@ -11121,12 +11121,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -11150,55 +11150,55 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.846</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
@@ -11208,55 +11208,55 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.833</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11266,7 +11266,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -11295,12 +11295,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
@@ -11324,7 +11324,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -11353,12 +11353,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
@@ -11382,26 +11382,26 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11411,84 +11411,84 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
@@ -11498,12 +11498,12 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -11527,26 +11527,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11556,26 +11556,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -11585,7 +11585,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -11614,12 +11614,12 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G78" s="6" t="n">
@@ -11643,12 +11643,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
@@ -11672,26 +11672,26 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
@@ -11701,26 +11701,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11730,26 +11730,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11759,12 +11759,12 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11788,26 +11788,26 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11817,26 +11817,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E85" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11846,26 +11846,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11875,26 +11875,26 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E87" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11904,26 +11904,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11933,29 +11933,58 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
+          <t>黒の太陽</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>AlmaVivaJP</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n">
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>AlmaVivaJP</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12020,7 +12049,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0844</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="3">
@@ -12036,7 +12065,7 @@
         <v>421</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2018</v>
+        <v>0.2016</v>
       </c>
     </row>
     <row r="4">
@@ -12052,7 +12081,7 @@
         <v>872</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.418</v>
+        <v>0.4176</v>
       </c>
     </row>
     <row r="5">
@@ -12065,10 +12094,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0791</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="6">
@@ -12084,7 +12113,7 @@
         <v>452</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2167</v>
+        <v>0.2165</v>
       </c>
     </row>
   </sheetData>
@@ -16016,7 +16045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O180"/>
+  <dimension ref="A1:P180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16033,7 +16062,8 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16109,6 +16139,11 @@
       </c>
       <c r="O1" s="4" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
@@ -16159,6 +16194,9 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>159</v>
       </c>
     </row>
@@ -16208,6 +16246,9 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
         <v>157</v>
       </c>
     </row>
@@ -16257,7 +16298,10 @@
         <v>13</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>147</v>
+        <v>1</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="5">
@@ -16306,6 +16350,9 @@
         <v>10</v>
       </c>
       <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>146</v>
       </c>
     </row>
@@ -16355,6 +16402,9 @@
         <v>16</v>
       </c>
       <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
         <v>144</v>
       </c>
     </row>
@@ -16404,6 +16454,9 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
         <v>137</v>
       </c>
     </row>
@@ -16453,6 +16506,9 @@
         <v>7</v>
       </c>
       <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
         <v>136</v>
       </c>
     </row>
@@ -16502,6 +16558,9 @@
         <v>10</v>
       </c>
       <c r="O9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5" t="n">
         <v>135</v>
       </c>
     </row>
@@ -16551,6 +16610,9 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>128</v>
       </c>
     </row>
@@ -16600,6 +16662,9 @@
         <v>8</v>
       </c>
       <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
         <v>127</v>
       </c>
     </row>
@@ -16649,6 +16714,9 @@
         <v>10</v>
       </c>
       <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>126</v>
       </c>
     </row>
@@ -16698,6 +16766,9 @@
         <v>0</v>
       </c>
       <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
         <v>125</v>
       </c>
     </row>
@@ -16747,6 +16818,9 @@
         <v>14</v>
       </c>
       <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
         <v>124</v>
       </c>
     </row>
@@ -16796,6 +16870,9 @@
         <v>12</v>
       </c>
       <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>120</v>
       </c>
     </row>
@@ -16845,6 +16922,9 @@
         <v>14</v>
       </c>
       <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>120</v>
       </c>
     </row>
@@ -16894,6 +16974,9 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>118</v>
       </c>
     </row>
@@ -16943,7 +17026,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="19">
@@ -16992,6 +17078,9 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>110</v>
       </c>
     </row>
@@ -17041,6 +17130,9 @@
         <v>0</v>
       </c>
       <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>110</v>
       </c>
     </row>
@@ -17090,7 +17182,10 @@
         <v>9</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="22">
@@ -17139,6 +17234,9 @@
         <v>0</v>
       </c>
       <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -17188,6 +17286,9 @@
         <v>10</v>
       </c>
       <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -17237,6 +17338,9 @@
         <v>6</v>
       </c>
       <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
         <v>104</v>
       </c>
     </row>
@@ -17286,6 +17390,9 @@
         <v>9</v>
       </c>
       <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5" t="n">
         <v>104</v>
       </c>
     </row>
@@ -17335,6 +17442,9 @@
         <v>6</v>
       </c>
       <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
         <v>103</v>
       </c>
     </row>
@@ -17384,6 +17494,9 @@
         <v>8</v>
       </c>
       <c r="O27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="5" t="n">
         <v>102</v>
       </c>
     </row>
@@ -17433,154 +17546,166 @@
         <v>7</v>
       </c>
       <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="5" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" s="5" t="n">
+      <c r="L30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="H31" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="K31" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>95</v>
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="32">
@@ -17629,6 +17754,9 @@
         <v>9</v>
       </c>
       <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
         <v>90</v>
       </c>
     </row>
@@ -17678,6 +17806,9 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
         <v>88</v>
       </c>
     </row>
@@ -17727,6 +17858,9 @@
         <v>6</v>
       </c>
       <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
         <v>86</v>
       </c>
     </row>
@@ -17776,6 +17910,9 @@
         <v>5</v>
       </c>
       <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
         <v>81</v>
       </c>
     </row>
@@ -17825,7 +17962,10 @@
         <v>12</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="37">
@@ -17874,7 +18014,10 @@
         <v>16</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="38">
@@ -17923,6 +18066,9 @@
         <v>2</v>
       </c>
       <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
         <v>77</v>
       </c>
     </row>
@@ -17972,6 +18118,9 @@
         <v>0</v>
       </c>
       <c r="O39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5" t="n">
         <v>76</v>
       </c>
     </row>
@@ -18021,6 +18170,9 @@
         <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
         <v>74</v>
       </c>
     </row>
@@ -18070,6 +18222,9 @@
         <v>12</v>
       </c>
       <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5" t="n">
         <v>73</v>
       </c>
     </row>
@@ -18119,6 +18274,9 @@
         <v>4</v>
       </c>
       <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
         <v>67</v>
       </c>
     </row>
@@ -18168,6 +18326,9 @@
         <v>6</v>
       </c>
       <c r="O43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="5" t="n">
         <v>66</v>
       </c>
     </row>
@@ -18217,6 +18378,9 @@
         <v>9</v>
       </c>
       <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
         <v>66</v>
       </c>
     </row>
@@ -18266,6 +18430,9 @@
         <v>3</v>
       </c>
       <c r="O45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="5" t="n">
         <v>65</v>
       </c>
     </row>
@@ -18315,153 +18482,165 @@
         <v>6</v>
       </c>
       <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>SЕRЕNIТY</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L48" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -18511,6 +18690,9 @@
         <v>0</v>
       </c>
       <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
         <v>56</v>
       </c>
     </row>
@@ -18560,6 +18742,9 @@
         <v>0</v>
       </c>
       <c r="O51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5" t="n">
         <v>54</v>
       </c>
     </row>
@@ -18609,6 +18794,9 @@
         <v>5</v>
       </c>
       <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
         <v>54</v>
       </c>
     </row>
@@ -18658,6 +18846,9 @@
         <v>1</v>
       </c>
       <c r="O53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="5" t="n">
         <v>53</v>
       </c>
     </row>
@@ -18707,6 +18898,9 @@
         <v>4</v>
       </c>
       <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
         <v>52</v>
       </c>
     </row>
@@ -18756,6 +18950,9 @@
         <v>10</v>
       </c>
       <c r="O55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="5" t="n">
         <v>51</v>
       </c>
     </row>
@@ -18805,6 +19002,9 @@
         <v>0</v>
       </c>
       <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
         <v>46</v>
       </c>
     </row>
@@ -18854,6 +19054,9 @@
         <v>0</v>
       </c>
       <c r="O57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="5" t="n">
         <v>44</v>
       </c>
     </row>
@@ -18903,6 +19106,9 @@
         <v>0</v>
       </c>
       <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
         <v>41</v>
       </c>
     </row>
@@ -18952,6 +19158,9 @@
         <v>0</v>
       </c>
       <c r="O59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="5" t="n">
         <v>39</v>
       </c>
     </row>
@@ -19001,6 +19210,9 @@
         <v>0</v>
       </c>
       <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
         <v>37</v>
       </c>
     </row>
@@ -19050,6 +19262,9 @@
         <v>0</v>
       </c>
       <c r="O61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="5" t="n">
         <v>36</v>
       </c>
     </row>
@@ -19099,6 +19314,9 @@
         <v>1</v>
       </c>
       <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -19148,6 +19366,9 @@
         <v>0</v>
       </c>
       <c r="O63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -19197,6 +19418,9 @@
         <v>1</v>
       </c>
       <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -19246,6 +19470,9 @@
         <v>0</v>
       </c>
       <c r="O65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -19295,6 +19522,9 @@
         <v>0</v>
       </c>
       <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
         <v>33</v>
       </c>
     </row>
@@ -19344,6 +19574,9 @@
         <v>13</v>
       </c>
       <c r="O67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="5" t="n">
         <v>32</v>
       </c>
     </row>
@@ -19393,6 +19626,9 @@
         <v>11</v>
       </c>
       <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
         <v>30</v>
       </c>
     </row>
@@ -19442,6 +19678,9 @@
         <v>0</v>
       </c>
       <c r="O69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="5" t="n">
         <v>30</v>
       </c>
     </row>
@@ -19491,6 +19730,9 @@
         <v>1</v>
       </c>
       <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
         <v>29</v>
       </c>
     </row>
@@ -19540,6 +19782,9 @@
         <v>2</v>
       </c>
       <c r="O71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -19589,6 +19834,9 @@
         <v>1</v>
       </c>
       <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -19638,6 +19886,9 @@
         <v>3</v>
       </c>
       <c r="O73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -19687,6 +19938,9 @@
         <v>2</v>
       </c>
       <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -19736,6 +19990,9 @@
         <v>0</v>
       </c>
       <c r="O75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -19785,6 +20042,9 @@
         <v>1</v>
       </c>
       <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="5" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19834,6 +20094,9 @@
         <v>3</v>
       </c>
       <c r="O77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="5" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19883,6 +20146,9 @@
         <v>0</v>
       </c>
       <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -19932,6 +20198,9 @@
         <v>4</v>
       </c>
       <c r="O79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -19981,6 +20250,9 @@
         <v>0</v>
       </c>
       <c r="O80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20030,6 +20302,9 @@
         <v>0</v>
       </c>
       <c r="O81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20079,6 +20354,9 @@
         <v>8</v>
       </c>
       <c r="O82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -20128,6 +20406,9 @@
         <v>0</v>
       </c>
       <c r="O83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -20177,6 +20458,9 @@
         <v>4</v>
       </c>
       <c r="O84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -20226,6 +20510,9 @@
         <v>0</v>
       </c>
       <c r="O85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="5" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20275,7 +20562,10 @@
         <v>2</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="P86" s="5" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -20324,6 +20614,9 @@
         <v>0</v>
       </c>
       <c r="O87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20373,6 +20666,9 @@
         <v>0</v>
       </c>
       <c r="O88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20422,6 +20718,9 @@
         <v>1</v>
       </c>
       <c r="O89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20471,6 +20770,9 @@
         <v>0</v>
       </c>
       <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20520,6 +20822,9 @@
         <v>2</v>
       </c>
       <c r="O91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -20569,6 +20874,9 @@
         <v>0</v>
       </c>
       <c r="O92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -20618,6 +20926,9 @@
         <v>0</v>
       </c>
       <c r="O93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -20667,6 +20978,9 @@
         <v>0</v>
       </c>
       <c r="O94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -20716,6 +21030,9 @@
         <v>0</v>
       </c>
       <c r="O95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -20765,6 +21082,9 @@
         <v>0</v>
       </c>
       <c r="O96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20814,6 +21134,9 @@
         <v>0</v>
       </c>
       <c r="O97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20863,6 +21186,9 @@
         <v>1</v>
       </c>
       <c r="O98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20912,6 +21238,9 @@
         <v>0</v>
       </c>
       <c r="O99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20961,6 +21290,9 @@
         <v>0</v>
       </c>
       <c r="O100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21010,6 +21342,9 @@
         <v>0</v>
       </c>
       <c r="O101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21059,6 +21394,9 @@
         <v>2</v>
       </c>
       <c r="O102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21108,6 +21446,9 @@
         <v>2</v>
       </c>
       <c r="O103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21157,6 +21498,9 @@
         <v>0</v>
       </c>
       <c r="O104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21206,6 +21550,9 @@
         <v>0</v>
       </c>
       <c r="O105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21255,6 +21602,9 @@
         <v>0</v>
       </c>
       <c r="O106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21304,6 +21654,9 @@
         <v>0</v>
       </c>
       <c r="O107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21353,6 +21706,9 @@
         <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21402,6 +21758,9 @@
         <v>0</v>
       </c>
       <c r="O109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21451,6 +21810,9 @@
         <v>0</v>
       </c>
       <c r="O110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21500,6 +21862,9 @@
         <v>2</v>
       </c>
       <c r="O111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21549,6 +21914,9 @@
         <v>0</v>
       </c>
       <c r="O112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21598,6 +21966,9 @@
         <v>1</v>
       </c>
       <c r="O113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21647,6 +22018,9 @@
         <v>0</v>
       </c>
       <c r="O114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21696,6 +22070,9 @@
         <v>0</v>
       </c>
       <c r="O115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21745,6 +22122,9 @@
         <v>0</v>
       </c>
       <c r="O116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21794,6 +22174,9 @@
         <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21843,6 +22226,9 @@
         <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21892,6 +22278,9 @@
         <v>0</v>
       </c>
       <c r="O119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21941,6 +22330,9 @@
         <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21990,6 +22382,9 @@
         <v>0</v>
       </c>
       <c r="O121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22039,6 +22434,9 @@
         <v>0</v>
       </c>
       <c r="O122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22088,6 +22486,9 @@
         <v>0</v>
       </c>
       <c r="O123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22137,6 +22538,9 @@
         <v>0</v>
       </c>
       <c r="O124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22186,6 +22590,9 @@
         <v>0</v>
       </c>
       <c r="O125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22235,6 +22642,9 @@
         <v>0</v>
       </c>
       <c r="O126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22284,6 +22694,9 @@
         <v>0</v>
       </c>
       <c r="O127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22333,6 +22746,9 @@
         <v>0</v>
       </c>
       <c r="O128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22382,6 +22798,9 @@
         <v>0</v>
       </c>
       <c r="O129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22431,6 +22850,9 @@
         <v>0</v>
       </c>
       <c r="O130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22480,6 +22902,9 @@
         <v>0</v>
       </c>
       <c r="O131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22529,6 +22954,9 @@
         <v>0</v>
       </c>
       <c r="O132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22578,6 +23006,9 @@
         <v>1</v>
       </c>
       <c r="O133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22627,6 +23058,9 @@
         <v>0</v>
       </c>
       <c r="O134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22676,6 +23110,9 @@
         <v>0</v>
       </c>
       <c r="O135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22725,6 +23162,9 @@
         <v>3</v>
       </c>
       <c r="O136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22774,6 +23214,9 @@
         <v>0</v>
       </c>
       <c r="O137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22823,6 +23266,9 @@
         <v>0</v>
       </c>
       <c r="O138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22872,6 +23318,9 @@
         <v>2</v>
       </c>
       <c r="O139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22921,6 +23370,9 @@
         <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22970,6 +23422,9 @@
         <v>0</v>
       </c>
       <c r="O141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23019,6 +23474,9 @@
         <v>0</v>
       </c>
       <c r="O142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23068,6 +23526,9 @@
         <v>0</v>
       </c>
       <c r="O143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23117,6 +23578,9 @@
         <v>0</v>
       </c>
       <c r="O144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23166,6 +23630,9 @@
         <v>0</v>
       </c>
       <c r="O145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23215,6 +23682,9 @@
         <v>0</v>
       </c>
       <c r="O146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23264,6 +23734,9 @@
         <v>1</v>
       </c>
       <c r="O147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23313,6 +23786,9 @@
         <v>0</v>
       </c>
       <c r="O148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23362,6 +23838,9 @@
         <v>2</v>
       </c>
       <c r="O149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23411,6 +23890,9 @@
         <v>0</v>
       </c>
       <c r="O150" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23460,6 +23942,9 @@
         <v>0</v>
       </c>
       <c r="O151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23509,6 +23994,9 @@
         <v>0</v>
       </c>
       <c r="O152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23558,6 +24046,9 @@
         <v>2</v>
       </c>
       <c r="O153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23607,6 +24098,9 @@
         <v>0</v>
       </c>
       <c r="O154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23656,6 +24150,9 @@
         <v>0</v>
       </c>
       <c r="O155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23705,6 +24202,9 @@
         <v>0</v>
       </c>
       <c r="O156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23754,6 +24254,9 @@
         <v>0</v>
       </c>
       <c r="O157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23803,6 +24306,9 @@
         <v>0</v>
       </c>
       <c r="O158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23852,6 +24358,9 @@
         <v>0</v>
       </c>
       <c r="O159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23901,6 +24410,9 @@
         <v>0</v>
       </c>
       <c r="O160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23950,6 +24462,9 @@
         <v>0</v>
       </c>
       <c r="O161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23999,6 +24514,9 @@
         <v>0</v>
       </c>
       <c r="O162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24048,6 +24566,9 @@
         <v>0</v>
       </c>
       <c r="O163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24097,6 +24618,9 @@
         <v>0</v>
       </c>
       <c r="O164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24146,6 +24670,9 @@
         <v>0</v>
       </c>
       <c r="O165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24195,6 +24722,9 @@
         <v>0</v>
       </c>
       <c r="O166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24244,6 +24774,9 @@
         <v>0</v>
       </c>
       <c r="O167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24293,6 +24826,9 @@
         <v>0</v>
       </c>
       <c r="O168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24342,6 +24878,9 @@
         <v>0</v>
       </c>
       <c r="O169" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24391,6 +24930,9 @@
         <v>0</v>
       </c>
       <c r="O170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24440,6 +24982,9 @@
         <v>0</v>
       </c>
       <c r="O171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24489,6 +25034,9 @@
         <v>1</v>
       </c>
       <c r="O172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24538,6 +25086,9 @@
         <v>1</v>
       </c>
       <c r="O173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24587,6 +25138,9 @@
         <v>0</v>
       </c>
       <c r="O174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24636,6 +25190,9 @@
         <v>1</v>
       </c>
       <c r="O175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24685,6 +25242,9 @@
         <v>0</v>
       </c>
       <c r="O176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24734,6 +25294,9 @@
         <v>0</v>
       </c>
       <c r="O177" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24783,6 +25346,9 @@
         <v>0</v>
       </c>
       <c r="O178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24832,6 +25398,9 @@
         <v>1</v>
       </c>
       <c r="O179" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24881,6 +25450,9 @@
         <v>0</v>
       </c>
       <c r="O180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24895,7 +25467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24917,12 +25489,12 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>前半参加数(2025-08〜2026-01)</t>
+          <t>前半参加数(2025-08〜2026-02)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>後半参加数(2026-02〜2026-08)</t>
+          <t>後半参加数(2026-03〜2026-09)</t>
         </is>
       </c>
     </row>
@@ -24965,7 +25537,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -24977,13 +25549,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -25001,7 +25573,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25013,13 +25585,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25037,25 +25609,25 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新規参入(後半のみ)</t>
+          <t>離脱(前半のみ)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -25064,7 +25636,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
@@ -25073,7 +25645,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -25082,7 +25654,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
@@ -25091,7 +25663,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -25100,7 +25672,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0</v>
@@ -25109,7 +25681,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>DoraemonSA</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -25118,7 +25690,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
@@ -25127,7 +25699,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -25136,7 +25708,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -25145,7 +25717,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>DoraemonSA</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -25154,7 +25726,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -25163,7 +25735,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>愛Eиdorphiиe</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -25172,7 +25744,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -25181,7 +25753,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -25190,7 +25762,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -25199,7 +25771,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>愛Eиdorphiиe</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -25208,7 +25780,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -25217,7 +25789,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -25226,7 +25798,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
@@ -25235,7 +25807,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -25244,7 +25816,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -25253,7 +25825,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -25262,7 +25834,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -25271,7 +25843,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -25280,7 +25852,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -25289,7 +25861,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -25298,7 +25870,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
@@ -25307,7 +25879,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -25316,7 +25888,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -25325,7 +25897,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -25334,7 +25906,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>0</v>
@@ -25343,7 +25915,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -25352,7 +25924,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -25361,7 +25933,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -25370,7 +25942,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
@@ -25379,7 +25951,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -25388,7 +25960,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
@@ -25397,7 +25969,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -25415,7 +25987,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -25424,7 +25996,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>0</v>
@@ -25433,7 +26005,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -25442,7 +26014,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>0</v>
@@ -25451,7 +26023,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -25469,7 +26041,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -25487,7 +26059,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -25496,7 +26068,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>0</v>
@@ -25505,7 +26077,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -25514,7 +26086,7 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>0</v>
@@ -25523,7 +26095,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -25535,6 +26107,42 @@
         <v>5</v>
       </c>
       <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>TRAITORsJP</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>離脱(前半のみ)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Ancîеnts</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>離脱(前半のみ)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25895,16 +26503,16 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Unity(29), 黒の太陽(19), シェイド(18), xAEGISx(14), ーリベリオンー(12), FLORISTS(12), Phoenix(12), 一Arch(11)</t>
+          <t>Unity(29), 黒の太陽(20), シェイド(19), xAEGISx(15), ーリベリオンー(12), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽(7勝), シェイド(6勝), xAEGISx(5勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
+          <t>黒の太陽(7勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
         </is>
       </c>
     </row>
@@ -26194,16 +26802,16 @@
         <v>35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(26), RaиkSS(20), 雲淡風輕o(17), 當惡魔遇到殺手貓(15), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
+          <t>PONYTAIL(27), RaиkSS(20), 雲淡風輕o(17), 當惡魔遇到殺手貓(16), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(23勝), RaиkSS(16勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
+          <t>PONYTAIL(24勝), RaиkSS(16勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2088</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>54</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3396</v>
+        <v>0.3375</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1944</v>
+        <v>0.1931</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>20</v>
@@ -771,51 +771,51 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>136</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.3529</v>
+        <v>0.3309</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>84</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.3529</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>84</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1296,51 +1296,51 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.3646</v>
+        <v>0.1443</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
         <v>96</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.1458</v>
+        <v>0.3646</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.2778</v>
+        <v>0.2857</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
@@ -1400,19 +1400,19 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3295</v>
+        <v>0.3371</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
@@ -1621,51 +1621,51 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
         <v>67</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1493</v>
+        <v>0.7164</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.7121</v>
+        <v>0.1493</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.1364</v>
+        <v>0.1343</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>22</v>
@@ -1696,51 +1696,51 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.6818</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
         <v>65</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.1692</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1846,51 +1846,51 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.5636</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.5556</v>
+        <v>0.2222</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1950,19 +1950,19 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.1961</v>
+        <v>0.2115</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C76" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.1304</v>
+        <v>0.125</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>0</v>
@@ -2521,51 +2521,51 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>SanctaTerra</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>SanctaTerra</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
         <v>21</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1429</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>34</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3271,48 +3271,48 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0</v>
@@ -3321,20 +3321,20 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.1429</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>13</v>
@@ -3346,23 +3346,23 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>0</v>
@@ -3371,51 +3371,51 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -3696,23 +3696,23 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>0</v>
@@ -3721,17 +3721,17 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E126" s="5" t="n">
         <v>4</v>
@@ -3746,23 +3746,23 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -3784,10 +3784,10 @@
         <v>0.5</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0</v>
@@ -3796,23 +3796,23 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G129" s="5" t="n">
         <v>0</v>
@@ -3821,23 +3821,23 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G130" s="5" t="n">
         <v>0</v>
@@ -3846,23 +3846,23 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G131" s="5" t="n">
         <v>0</v>
@@ -3871,23 +3871,23 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E132" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G132" s="5" t="n">
         <v>0</v>
@@ -3896,11 +3896,11 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C133" s="5" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
         <v>3</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0</v>
@@ -4446,17 +4446,17 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" s="5" t="n">
         <v>2</v>
@@ -4471,23 +4471,23 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G156" s="5" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
@@ -4512,7 +4512,7 @@
         <v>2</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G157" s="5" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
@@ -4537,7 +4537,7 @@
         <v>2</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G158" s="5" t="n">
         <v>0</v>
@@ -4546,23 +4546,23 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G159" s="5" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
@@ -4587,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>0</v>
@@ -4596,17 +4596,17 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E161" s="5" t="n">
         <v>1</v>
@@ -4621,7 +4621,7 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -4637,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G162" s="5" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -4662,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G163" s="5" t="n">
         <v>0</v>
@@ -4671,7 +4671,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -4696,7 +4696,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -4712,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G165" s="5" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -4746,7 +4746,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -4771,7 +4771,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G168" s="5" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -4812,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G169" s="5" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="5" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -5071,25 +5071,50 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
+          <t>VIRULENT死</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
           <t>PinöyPioneer</t>
         </is>
       </c>
-      <c r="B180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" s="5" t="n">
+      <c r="B181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5216,10 +5241,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>21</v>
@@ -5585,64 +5610,64 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -5837,22 +5862,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -5863,28 +5888,28 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -5894,76 +5919,76 @@
         <v>1</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -5975,31 +6000,31 @@
         <v>20</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -6488,19 +6513,19 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>3</v>
@@ -6509,169 +6534,169 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -7811,54 +7836,54 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
@@ -7868,60 +7893,60 @@
         <v>3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
@@ -7937,12 +7962,12 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
@@ -7952,34 +7977,34 @@
         <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -7991,52 +8016,52 @@
         <v>11</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
           <t>義勇</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -8047,7 +8072,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
@@ -8057,91 +8082,91 @@
         <v>1</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -8152,14 +8177,14 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E145" s="5" t="n">
         <v>3</v>
@@ -8168,112 +8193,112 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
           <t>柿一門</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -8288,39 +8313,39 @@
         <v>3</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
@@ -8330,81 +8355,81 @@
         <v>4</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
@@ -8414,18 +8439,18 @@
         <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
@@ -8435,7 +8460,7 @@
         <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159">
@@ -10947,12 +10972,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
@@ -10966,7 +10991,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
@@ -10976,70 +11001,70 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -11053,7 +11078,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
@@ -11063,12 +11088,12 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
@@ -11082,7 +11107,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
@@ -11092,26 +11117,26 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
@@ -11121,12 +11146,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -11140,7 +11165,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -12049,7 +12074,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0843</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -12062,10 +12087,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2016</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="4">
@@ -12078,10 +12103,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4176</v>
+        <v>0.4174</v>
       </c>
     </row>
     <row r="5">
@@ -12097,7 +12122,7 @@
         <v>167</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.08</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="6">
@@ -12110,10 +12135,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2165</v>
+        <v>0.2163</v>
       </c>
     </row>
   </sheetData>
@@ -12127,7 +12152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13653,7 +13678,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、溫柔鄉</t>
+          <t>Döraè่mön、美孚冰室</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -13661,7 +13686,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13701,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PONYTAIL</t>
+          <t>微笑Party、溫柔鄉</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -13684,30 +13709,30 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Maverickz、PONYTAIL</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13722,15 +13747,15 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
+          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
+          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
         </is>
       </c>
     </row>
@@ -13745,15 +13770,15 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:5勝, Kopitiam:5勝, MelonEmpire:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
         </is>
       </c>
     </row>
@@ -13768,15 +13793,15 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、TRAITORs</t>
+          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
+          <t>亗Luxúria亗:5勝, Kopitiam:5勝, MelonEmpire:3勝</t>
         </is>
       </c>
     </row>
@@ -13791,15 +13816,15 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
+          <t>PONYTAIL、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
+          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -13814,15 +13839,15 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13862,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
@@ -13845,7 +13870,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -13860,15 +13885,15 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -13883,7 +13908,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
@@ -13891,7 +13916,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -13906,7 +13931,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
@@ -13914,7 +13939,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13954,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -13937,7 +13962,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13977,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -13960,7 +13985,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -13975,7 +14000,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -13983,7 +14008,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -13998,7 +14023,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -14006,7 +14031,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:4勝</t>
+          <t>RaиkSS:4勝</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14046,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14029,7 +14054,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
+          <t>沙漠黑鷹:4勝</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14069,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、PONYTAIL</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -14052,7 +14077,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝</t>
+          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14092,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、PONYTAIL</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14075,7 +14100,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:4勝</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14115,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14098,7 +14123,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, RaиkSS:2勝</t>
+          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14138,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14121,7 +14146,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>VainqueurJP:2勝, RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -14136,15 +14161,15 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14184,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14167,7 +14192,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14207,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -14190,7 +14215,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14230,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
@@ -14213,7 +14238,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14253,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -14236,7 +14261,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14276,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
@@ -14259,7 +14284,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14299,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -14282,7 +14307,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14322,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14305,7 +14330,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14345,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14328,7 +14353,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14343,15 +14368,15 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14391,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14374,7 +14399,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14414,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14397,7 +14422,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14437,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14420,7 +14445,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14460,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14443,7 +14468,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14483,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14481,7 +14506,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14489,7 +14514,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14529,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14512,7 +14537,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14552,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14535,7 +14560,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14550,7 +14575,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14558,7 +14583,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14598,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14581,7 +14606,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14621,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14604,7 +14629,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14644,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14627,7 +14652,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14667,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14650,7 +14675,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14690,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14673,7 +14698,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14713,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14696,7 +14721,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14736,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14719,7 +14744,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14759,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14742,7 +14767,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14782,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14765,7 +14790,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14805,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14788,7 +14813,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14828,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14811,7 +14836,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -14826,7 +14851,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14834,7 +14859,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14874,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14857,7 +14882,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14897,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14880,7 +14905,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14920,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -14903,7 +14928,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14943,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14926,7 +14951,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14966,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -14949,7 +14974,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -14964,7 +14989,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14972,7 +14997,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -14987,7 +15012,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -14995,7 +15020,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15035,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15018,7 +15043,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15058,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15056,7 +15081,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15064,7 +15089,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15104,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15087,7 +15112,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15127,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15110,7 +15135,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15150,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15133,7 +15158,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15173,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15156,7 +15181,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15196,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15179,7 +15204,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15219,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15202,7 +15227,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15217,7 +15242,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15225,7 +15250,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15265,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15248,7 +15273,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15288,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15271,7 +15296,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15311,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15294,7 +15319,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15334,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15317,7 +15342,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15357,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15340,7 +15365,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15380,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15363,7 +15388,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15403,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15386,7 +15411,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15426,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15409,7 +15434,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15424,7 +15449,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15432,7 +15457,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15472,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15455,7 +15480,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15495,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15478,7 +15503,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15518,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15501,30 +15526,30 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15539,15 +15564,15 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15587,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15570,7 +15595,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15585,15 +15610,15 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15633,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15616,7 +15641,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15656,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
@@ -15639,7 +15664,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15679,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -15662,7 +15687,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15702,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
@@ -15700,7 +15725,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -15708,7 +15733,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15748,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15731,7 +15756,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15771,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15754,30 +15779,30 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:4勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -15792,15 +15817,15 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:4勝</t>
         </is>
       </c>
     </row>
@@ -15815,7 +15840,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15838,7 +15863,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15861,7 +15886,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
@@ -15884,7 +15909,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -15892,7 +15917,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15907,7 +15932,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -15915,7 +15940,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15955,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -15953,7 +15978,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -15961,7 +15986,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -15976,7 +16001,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -15984,7 +16009,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -15999,7 +16024,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16022,13 +16047,36 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D169" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
+      <c r="D170" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16045,7 +16093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P180"/>
+  <dimension ref="A1:P181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16194,10 +16242,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -16402,10 +16450,10 @@
         <v>16</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -16463,50 +16511,50 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>11</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>136</v>
@@ -16515,53 +16563,53 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>11</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>12</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -17555,102 +17603,102 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="L29" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>96</v>
@@ -17754,10 +17802,10 @@
         <v>9</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
@@ -17806,10 +17854,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34">
@@ -18231,50 +18279,50 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="5" t="n">
         <v>67</v>
@@ -18283,53 +18331,53 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="H43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="K43" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44">
@@ -18378,108 +18426,108 @@
         <v>9</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>3</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="L46" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M46" s="5" t="n">
         <v>3</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -18699,99 +18747,99 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="H51" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="I51" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J51" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L51" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="J52" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O52" s="5" t="n">
         <v>0</v>
@@ -18950,10 +18998,10 @@
         <v>10</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56">
@@ -20042,10 +20090,10 @@
         <v>1</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
@@ -20103,32 +20151,32 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>SanctaTerra</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>0</v>
@@ -20137,50 +20185,50 @@
         <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>SanctaTerra</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C79" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5" t="n">
         <v>0</v>
@@ -20189,13 +20237,13 @@
         <v>0</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O79" s="5" t="n">
         <v>0</v>
@@ -21663,11 +21711,11 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" s="5" t="n">
         <v>0</v>
@@ -21682,22 +21730,22 @@
         <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0</v>
@@ -21706,20 +21754,20 @@
         <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C109" s="5" t="n">
         <v>0</v>
@@ -21740,22 +21788,22 @@
         <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="5" t="n">
         <v>0</v>
@@ -21767,11 +21815,11 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C110" s="5" t="n">
         <v>0</v>
@@ -21798,10 +21846,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0</v>
@@ -21819,17 +21867,17 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>0</v>
@@ -21850,16 +21898,16 @@
         <v>0</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O111" s="5" t="n">
         <v>0</v>
@@ -21871,17 +21919,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -21902,16 +21950,16 @@
         <v>0</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>0</v>
@@ -21923,14 +21971,14 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>0</v>
@@ -21942,13 +21990,13 @@
         <v>0</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
         <v>0</v>
@@ -21957,13 +22005,13 @@
         <v>0</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
         <v>0</v>
@@ -22547,17 +22595,17 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>0</v>
@@ -22587,10 +22635,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" s="5" t="n">
         <v>4</v>
@@ -22599,14 +22647,14 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>0</v>
@@ -22651,14 +22699,14 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>0</v>
@@ -22703,14 +22751,14 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>0</v>
@@ -22755,20 +22803,20 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="5" t="n">
         <v>0</v>
@@ -22783,7 +22831,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" s="5" t="n">
         <v>0</v>
@@ -22807,23 +22855,23 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5" t="n">
         <v>0</v>
@@ -22835,13 +22883,13 @@
         <v>0</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="5" t="n">
         <v>0</v>
@@ -22859,23 +22907,23 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C131" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="5" t="n">
         <v>0</v>
@@ -22893,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="5" t="n">
         <v>0</v>
@@ -22911,14 +22959,14 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>0</v>
@@ -22936,16 +22984,16 @@
         <v>0</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="5" t="n">
         <v>0</v>
@@ -22963,17 +23011,17 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>0</v>
@@ -22988,28 +23036,28 @@
         <v>0</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -24107,11 +24155,11 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C155" s="5" t="n">
         <v>0</v>
@@ -24147,10 +24195,10 @@
         <v>0</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" s="5" t="n">
         <v>2</v>
@@ -24159,17 +24207,17 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" s="5" t="n">
         <v>0</v>
@@ -24211,17 +24259,17 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
         <v>0</v>
@@ -24263,17 +24311,17 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" s="5" t="n">
         <v>0</v>
@@ -24315,17 +24363,17 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
         <v>0</v>
@@ -24367,14 +24415,14 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>0</v>
@@ -24419,11 +24467,11 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="5" t="n">
         <v>0</v>
@@ -24465,13 +24513,13 @@
         <v>0</v>
       </c>
       <c r="P161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -24523,11 +24571,11 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" s="5" t="n">
         <v>0</v>
@@ -24542,7 +24590,7 @@
         <v>0</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="5" t="n">
         <v>0</v>
@@ -24575,7 +24623,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -24627,7 +24675,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -24679,14 +24727,14 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" s="5" t="n">
         <v>0</v>
@@ -24698,7 +24746,7 @@
         <v>0</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="5" t="n">
         <v>0</v>
@@ -24731,7 +24779,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -24783,14 +24831,14 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>0</v>
@@ -24835,11 +24883,11 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" s="5" t="n">
         <v>0</v>
@@ -24857,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="5" t="n">
         <v>0</v>
@@ -24887,7 +24935,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -24903,13 +24951,13 @@
         <v>0</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" s="5" t="n">
         <v>0</v>
@@ -24939,7 +24987,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -24991,7 +25039,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -25007,7 +25055,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -25031,7 +25079,7 @@
         <v>0</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" s="5" t="n">
         <v>0</v>
@@ -25407,52 +25455,104 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
+          <t>VIRULENT死</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
           <t>PinöyPioneer</t>
         </is>
       </c>
-      <c r="B180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="5" t="n">
+      <c r="B181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26201,14 +26301,14 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ーEspoirー(18), Revenant(16), C0BRA(15), SanctaTerra(14), EIemento(13), 厶pocalypse(13), Bagaиเ่(13), 柿一門(12)</t>
+          <t>ーEspoirー(18), Revenant(16), SanctaTerra(15), C0BRA(15), 厶pocalypse(14), EIemento(13), Bagaиเ่(13), 柿一門(12)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -26457,11 +26557,11 @@
         <v>46</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>一Arch(13), PokemonGo(12), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6), Revenant(6)</t>
+          <t>一Arch(13), PokemonGo(12), Maverickz(7), Döraè่mön(7), FLORISTS(6), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -26638,19 +26738,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(30), ßบรнíïdо丶ๅ家族(26), Kopitiam(24), MelonEmpire(9), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
+          <t>亗Luxúria亗(31), ßบรнíïdо丶ๅ家族(26), Kopitiam(25), MelonEmpire(9), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam(22勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
+          <t>Kopitiam(23勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
         </is>
       </c>
     </row>
@@ -26710,16 +26810,16 @@
         <v>23</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön(13), Phoenix(11), Myst(11), 微笑Party(7), VainqueurJP(6), 溫柔鄉(6), Иouver(5), 美孚冰室(4)</t>
+          <t>Döraè่mön(14), Phoenix(11), Myst(11), 微笑Party(7), VainqueurJP(6), 溫柔鄉(6), 美孚冰室(5), Иouver(5)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Myst(11勝), Phoenix(9勝), Döraè่mön(9勝), VainqueurJP(6勝), 雪狼族(3勝)</t>
+          <t>Myst(11勝), Döraè่mön(10勝), Phoenix(9勝), VainqueurJP(6勝), 雪狼族(3勝)</t>
         </is>
       </c>
     </row>
@@ -26753,19 +26853,19 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(18), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
+          <t>一惡人谷一(19), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(14勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
+          <t>一惡人谷一(15勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
         </is>
       </c>
     </row>
@@ -26986,16 +27086,16 @@
         <v>51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>柿一門(27), 義勇(21), 桜吹雪(18), 黄昏のえりしおん(16), ひよこりあ(16), Pandora(14), Restart(13), ZirconiA(11)</t>
+          <t>柿一門(28), 義勇(21), 桜吹雪(18), 黄昏のえりしおん(16), ひよこりあ(16), Pandora(15), Restart(14), 氣噗噗讓玻璃心碎一地(11)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>義勇(8勝), 柿一門(7勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝), Restart(3勝)</t>
+          <t>義勇(8勝), 柿一門(7勝), 氣噗噗讓玻璃心碎一地(4勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-03</t>
+          <t>2025-08-01 〜 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2094</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3376</v>
+        <v>0.3418</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1931</v>
+        <v>0.1918</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>20</v>
@@ -846,51 +846,51 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>127</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0.1102</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="F11" s="5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.1102</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.5806</v>
+        <v>0.584</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>17</v>
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.175</v>
+        <v>0.1736</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>32</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>2</v>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.2066</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>20</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5508</v>
+        <v>0.5462</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4775</v>
+        <v>0.469</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5182</v>
+        <v>0.5225</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1071,73 +1071,73 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.3818</v>
+        <v>0.5856</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
         <v>110</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.5909</v>
+        <v>0.3818</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4906</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>1</v>
@@ -1146,23 +1146,23 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4952</v>
+        <v>0.1429</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>1</v>
@@ -1171,51 +1171,51 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.4327</v>
+        <v>0.4857</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
         <v>104</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.4904</v>
+        <v>0.4327</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.6373</v>
+        <v>0.6311</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>10</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.2826</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>22</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.6914</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>9</v>
@@ -1471,51 +1471,51 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="F36" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
         <v>78</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.1795</v>
+        <v>0.2821</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1639</v>
+        <v>0.1613</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>5</v>
@@ -1900,19 +1900,19 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.1132</v>
+        <v>0.1111</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
@@ -1921,23 +1921,23 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.2885</v>
+        <v>0.2075</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -1946,23 +1946,23 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
         <v>52</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.2115</v>
+        <v>0.2885</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2500,19 +2500,19 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0.2273</v>
+        <v>0.2609</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>2</v>
@@ -2571,23 +2571,23 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>0</v>
@@ -2596,23 +2596,23 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>0</v>
@@ -2621,23 +2621,23 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>0.2632</v>
+        <v>0.1</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G82" s="5" t="n">
         <v>0</v>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C89" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.1333</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -3209,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>0</v>
@@ -3221,23 +3221,23 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0</v>
@@ -3246,23 +3246,23 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
@@ -3271,73 +3271,73 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,20 +3346,20 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.1429</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>13</v>
@@ -3371,23 +3371,23 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0</v>
@@ -3921,23 +3921,23 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="E134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
@@ -3946,23 +3946,23 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G135" s="5" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -3984,10 +3984,10 @@
         <v>0</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0</v>
@@ -3996,7 +3996,7 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -4012,7 +4012,7 @@
         <v>3</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G137" s="5" t="n">
         <v>0</v>
@@ -4021,23 +4021,23 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>HYLO匚乇尺乇u丂</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E138" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G138" s="5" t="n">
         <v>0</v>
@@ -4046,23 +4046,23 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G139" s="5" t="n">
         <v>0</v>
@@ -4071,11 +4071,11 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>M三OW</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C140" s="5" t="n">
         <v>0</v>
@@ -4084,10 +4084,10 @@
         <v>0</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>0</v>
@@ -4096,23 +4096,23 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>FestivalSA</t>
+          <t>HYLO匚乇尺乇u丂</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G141" s="5" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>DemiseSA</t>
+          <t>M三OW</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -4137,7 +4137,7 @@
         <v>2</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G142" s="5" t="n">
         <v>0</v>
@@ -4146,23 +4146,23 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>RevenantSA</t>
+          <t>FestivalSA</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G143" s="5" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>OBLIxVION</t>
+          <t>DemiseSA</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
@@ -4187,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G144" s="5" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>ZirconiAJP</t>
+          <t>RevenantSA</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
@@ -4212,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G145" s="5" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>DEMIG0DS</t>
+          <t>OBLIxVION</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G146" s="5" t="n">
         <v>0</v>
@@ -4246,7 +4246,7 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>ZirconiAJP</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
@@ -4262,7 +4262,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G147" s="5" t="n">
         <v>0</v>
@@ -4271,7 +4271,7 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>PinoyPioneer</t>
+          <t>DEMIG0DS</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
@@ -4296,23 +4296,23 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E149" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G149" s="5" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>죽음LC</t>
+          <t>PinoyPioneer</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -4337,7 +4337,7 @@
         <v>2</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G150" s="5" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>知音丶酒吧</t>
+          <t>죽음LC</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -4359,10 +4359,10 @@
         <v>0</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G151" s="5" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Kitanjou</t>
+          <t>知音丶酒吧</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
@@ -4384,10 +4384,10 @@
         <v>0</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G152" s="5" t="n">
         <v>0</v>
@@ -4396,20 +4396,20 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Kitanjou</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="5" t="n">
         <v>3</v>
@@ -4421,23 +4421,23 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>彡PAPAROCK彡</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G154" s="5" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>彡PAPAROCK彡</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
@@ -4462,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G155" s="5" t="n">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>46</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>43</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3</v>
@@ -5400,43 +5400,43 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>33</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6303,40 +6303,40 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>5</v>
@@ -6345,61 +6345,61 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>4</v>
@@ -6408,85 +6408,85 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -6660,7 +6660,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -6672,112 +6672,112 @@
         <v>16</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>4</v>
@@ -6786,49 +6786,49 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -6840,7 +6840,7 @@
         <v>16</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>0</v>
@@ -6849,33 +6849,33 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
@@ -6885,154 +6885,154 @@
         <v>5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
@@ -7416,33 +7416,33 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
@@ -7452,102 +7452,102 @@
         <v>4</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
@@ -7557,39 +7557,39 @@
         <v>2</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
@@ -7599,207 +7599,207 @@
         <v>2</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D119" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
@@ -7809,18 +7809,18 @@
         <v>2</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
@@ -7830,46 +7830,46 @@
         <v>3</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" s="5" t="n">
         <v>4</v>
@@ -7878,40 +7878,40 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="n">
         <v>4</v>
@@ -8613,7 +8613,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
         <v>10</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5" t="n">
         <v>1</v>
@@ -8634,28 +8634,28 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -8667,10 +8667,10 @@
         <v>10</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
@@ -8691,13 +8691,13 @@
         <v>3</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -8709,7 +8709,7 @@
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>0</v>
@@ -8718,75 +8718,75 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
@@ -8796,39 +8796,39 @@
         <v>2</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
@@ -8838,46 +8838,46 @@
         <v>1</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E177" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E178" s="5" t="n">
         <v>0</v>
@@ -8886,7 +8886,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -8907,40 +8907,40 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E181" s="5" t="n">
         <v>2</v>
@@ -8949,7 +8949,7 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -8964,13 +8964,13 @@
         <v>5</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E183" s="5" t="n">
         <v>3</v>
@@ -8991,12 +8991,12 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
@@ -9012,12 +9012,12 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
@@ -9027,81 +9027,81 @@
         <v>3</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
@@ -9111,25 +9111,25 @@
         <v>1</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
         <v>1</v>
@@ -9138,19 +9138,19 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E191" s="5" t="n">
         <v>1</v>
@@ -9580,12 +9580,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -9609,26 +9609,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
@@ -9638,26 +9638,26 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -12074,7 +12074,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0837</v>
       </c>
     </row>
     <row r="3">
@@ -12087,10 +12087,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2025</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="4">
@@ -12103,10 +12103,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4174</v>
+        <v>0.4175</v>
       </c>
     </row>
     <row r="5">
@@ -12119,10 +12119,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0798</v>
+        <v>0.0799</v>
       </c>
     </row>
     <row r="6">
@@ -12135,10 +12135,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2163</v>
+        <v>0.2159</v>
       </c>
     </row>
   </sheetData>
@@ -12152,7 +12152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Иouver、ーリベリオンー</t>
+          <t>ーリベリオンー、柿一門</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>cobraXverse、微笑Party</t>
+          <t>Иouver、ーリベリオンー</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, cobraXverse:1勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、雲淡風輕o</t>
+          <t>cobraXverse、微笑Party</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝</t>
+          <t>微笑Party:1勝, cobraXverse:1勝</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹</t>
+          <t>Phoenix、雲淡風輕o</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>Phoenix:2勝</t>
         </is>
       </c>
     </row>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Anino、ouтcasт</t>
+          <t>・殺戮・、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Anino:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Myst、VainqueurJP</t>
+          <t>Anino、ouтcasт</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Anino:2勝</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst</t>
+          <t>Myst、VainqueurJP</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Unity、海洋之心</t>
+          <t>Maverickz、Myst</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity</t>
+          <t>Unity、海洋之心</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、一DEFIANCE</t>
+          <t>Phoenix、Unity</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、Иouver</t>
+          <t>Maverickz、一DEFIANCE</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社、雲淡風輕o</t>
+          <t>VainqueurJP、Иouver</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Иouver、雲淡風輕o</t>
+          <t>東京熱株式會社、雲淡風輕o</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, Иouver:1勝</t>
+          <t>東京熱株式會社:2勝</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、VainqueurJP</t>
+          <t>Иouver、雲淡風輕o</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>雲淡風輕o:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Myst、Unity</t>
+          <t>Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Unity:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、Myst</t>
+          <t>Myst、Unity</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Etërnîty:1勝</t>
+          <t>Myst:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、SkyCastIe</t>
+          <t>Etërnîty、Myst</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:1勝, Maverickz:1勝</t>
+          <t>Myst:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ーリベリオンー</t>
+          <t>Maverickz、SkyCastIe</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>SkyCastIe:1勝, Maverickz:1勝</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、天機</t>
+          <t>xAEGISx、ーリベリオンー</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:2勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴</t>
+          <t>Etërnîty、天機</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 心晴:1勝</t>
+          <t>Etërnîty:2勝</t>
         </is>
       </c>
     </row>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
+          <t>天機、心晴</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地:2勝</t>
+          <t>天機:1勝, 心晴:1勝</t>
         </is>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、柿一門</t>
+          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo:2勝</t>
+          <t>氣噗噗讓玻璃心碎一地:2勝</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Myst</t>
+          <t>PokemonGo、柿一門</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>PokemonGo:2勝</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Myst、雲淡風輕o</t>
+          <t>Döraè่mön、Myst</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、微笑Party</t>
+          <t>Myst、雲淡風輕o</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、Vanartroops</t>
+          <t>Maverickz、微笑Party</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13287,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、溫柔鄉</t>
+          <t>SkyCastIe、Vanartroops</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>SkyCastIe:2勝</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、VainqueurJP</t>
+          <t>VainqueurJP、溫柔鄉</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>一SUN一、當惡魔遇到殺手貓</t>
+          <t>RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓</t>
+          <t>一SUN一、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、TRAITORs</t>
+          <t>RaиkSS、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PokemonGo</t>
+          <t>Maverickz、TRAITORs</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs</t>
+          <t>Maverickz、PokemonGo</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse</t>
+          <t>PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -13471,7 +13471,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Döraè่mön</t>
+          <t>Döraè่mön、cobraXverse</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、雲淡風輕o</t>
+          <t>AlmaVivaJP、Döraè่mön</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、心晴</t>
+          <t>VainqueurJP、雲淡風輕o</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Kaioken、TipsyTavern</t>
+          <t>PokemonGo、心晴</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>TipsyTavern:1勝, Kaioken:1勝</t>
+          <t>PokemonGo:2勝</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、一惡人谷一</t>
+          <t>Kaioken、TipsyTavern</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
+          <t>TipsyTavern:1勝, Kaioken:1勝</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、毛家村</t>
+          <t>Etërnîty、一惡人谷一</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>毛家村:2勝</t>
+          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>一DEFIANCE、雲淡風輕o</t>
+          <t>CatlandTHM、毛家村</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:2勝</t>
+          <t>毛家村:2勝</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>MÏRÃGË、雲淡風輕o</t>
+          <t>一DEFIANCE、雲淡風輕o</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
+          <t>雲淡風輕o:2勝</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、雲淡風輕o</t>
+          <t>MÏRÃGË、雲淡風輕o</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:2勝</t>
+          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、美孚冰室</t>
+          <t>CatlandTHM、雲淡風輕o</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝</t>
+          <t>雲淡風輕o:2勝</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、溫柔鄉</t>
+          <t>Döraè่mön、美孚冰室</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PONYTAIL</t>
+          <t>微笑Party、溫柔鄉</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
@@ -13732,30 +13732,30 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Maverickz、PONYTAIL</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13770,15 +13770,15 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
+          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
+          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
         </is>
       </c>
     </row>
@@ -13793,15 +13793,15 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:5勝, Kopitiam:5勝, MelonEmpire:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
         </is>
       </c>
     </row>
@@ -13816,15 +13816,15 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、TRAITORs</t>
+          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
+          <t>亗Luxúria亗:5勝, Kopitiam:5勝, MelonEmpire:3勝</t>
         </is>
       </c>
     </row>
@@ -13839,15 +13839,15 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
+          <t>PONYTAIL、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
+          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -13862,15 +13862,15 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -13908,15 +13908,15 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -13931,15 +13931,15 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:4勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
+          <t>RaиkSS:4勝</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、PONYTAIL</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝</t>
+          <t>沙漠黑鷹:4勝</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、PONYTAIL</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, RaиkSS:2勝</t>
+          <t>AlmaVivaJP:4勝</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14184,15 +14184,15 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14345,7 +14345,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14391,15 +14391,15 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15549,53 +15549,53 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15610,15 +15610,15 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15633,15 +15633,15 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15656,15 +15656,15 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15802,45 +15802,45 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:4勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15848,22 +15848,22 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -15886,15 +15886,15 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:4勝</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16070,13 +16070,82 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D170" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="D173" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16294,10 +16363,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
@@ -16450,10 +16519,10 @@
         <v>16</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -16667,50 +16736,50 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="J11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="O11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>127</v>
@@ -16719,53 +16788,53 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="G12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="K12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -16866,10 +16935,10 @@
         <v>14</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -16918,10 +16987,10 @@
         <v>12</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -16970,10 +17039,10 @@
         <v>14</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -17022,10 +17091,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
@@ -17074,10 +17143,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -17126,111 +17195,111 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>13</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>110</v>
@@ -17239,99 +17308,99 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>8</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O23" s="5" t="n">
         <v>0</v>
@@ -17343,99 +17412,99 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="E24" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>9</v>
       </c>
       <c r="H24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="J24" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>9</v>
       </c>
       <c r="H25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K25" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O25" s="5" t="n">
         <v>0</v>
@@ -17542,10 +17611,10 @@
         <v>8</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
@@ -17802,10 +17871,10 @@
         <v>9</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -17958,108 +18027,108 @@
         <v>5</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O37" s="5" t="n">
         <v>1</v>
@@ -18582,10 +18651,10 @@
         <v>10</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48">
@@ -18894,111 +18963,111 @@
         <v>1</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" s="5" t="n">
+      <c r="K54" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>5</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L55" s="5" t="n">
         <v>5</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" s="5" t="n">
         <v>52</v>
@@ -20142,10 +20211,10 @@
         <v>3</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
@@ -20255,50 +20324,50 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N80" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="O80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" s="5" t="n">
         <v>20</v>
@@ -20307,7 +20376,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -20317,16 +20386,16 @@
         <v>1</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>0</v>
@@ -20335,16 +20404,16 @@
         <v>0</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -20359,26 +20428,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>0</v>
@@ -20387,25 +20456,25 @@
         <v>0</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -20766,10 +20835,10 @@
         <v>1</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -21555,17 +21624,17 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -21577,28 +21646,28 @@
         <v>0</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105" s="5" t="n">
         <v>8</v>
@@ -21607,17 +21676,17 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0</v>
@@ -21629,13 +21698,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K106" s="5" t="n">
         <v>0</v>
@@ -21659,32 +21728,32 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
@@ -21711,29 +21780,29 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>1</v>
@@ -21745,16 +21814,16 @@
         <v>0</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108" s="5" t="n">
         <v>8</v>
@@ -21763,11 +21832,11 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" s="5" t="n">
         <v>0</v>
@@ -21782,22 +21851,22 @@
         <v>0</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>0</v>
@@ -21806,20 +21875,20 @@
         <v>1</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C110" s="5" t="n">
         <v>0</v>
@@ -21840,22 +21909,22 @@
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" s="5" t="n">
         <v>0</v>
@@ -21867,11 +21936,11 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C111" s="5" t="n">
         <v>0</v>
@@ -21898,10 +21967,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0</v>
@@ -21919,17 +21988,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -21950,16 +22019,16 @@
         <v>0</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>0</v>
@@ -23063,14 +23132,14 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>0</v>
@@ -23103,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P134" s="5" t="n">
         <v>3</v>
@@ -23115,11 +23184,11 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C135" s="5" t="n">
         <v>0</v>
@@ -23155,10 +23224,10 @@
         <v>0</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" s="5" t="n">
         <v>3</v>
@@ -23167,14 +23236,14 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>0</v>
@@ -23207,7 +23276,7 @@
         <v>0</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O136" s="5" t="n">
         <v>0</v>
@@ -23219,7 +23288,7 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -23238,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="5" t="n">
         <v>0</v>
@@ -23250,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="5" t="n">
         <v>0</v>
@@ -23259,10 +23328,10 @@
         <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P137" s="5" t="n">
         <v>3</v>
@@ -23271,11 +23340,11 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>HYLO匚乇尺乇u丂</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C138" s="5" t="n">
         <v>0</v>
@@ -23290,10 +23359,10 @@
         <v>0</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I138" s="5" t="n">
         <v>0</v>
@@ -23323,7 +23392,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
@@ -23363,19 +23432,19 @@
         <v>0</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O139" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>M三OW</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -23394,7 +23463,7 @@
         <v>0</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H140" s="5" t="n">
         <v>0</v>
@@ -23409,7 +23478,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="5" t="n">
         <v>0</v>
@@ -23421,20 +23490,20 @@
         <v>0</v>
       </c>
       <c r="P140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>FestivalSA</t>
+          <t>HYLO匚乇尺乇u丂</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>0</v>
@@ -23446,10 +23515,10 @@
         <v>0</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>0</v>
@@ -23473,17 +23542,17 @@
         <v>0</v>
       </c>
       <c r="P141" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>DemiseSA</t>
+          <t>M三OW</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C142" s="5" t="n">
         <v>0</v>
@@ -23510,10 +23579,10 @@
         <v>0</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="5" t="n">
         <v>0</v>
@@ -23531,14 +23600,14 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>RevenantSA</t>
+          <t>FestivalSA</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>0</v>
@@ -23583,11 +23652,11 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>OBLIxVION</t>
+          <t>DemiseSA</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C144" s="5" t="n">
         <v>0</v>
@@ -23596,7 +23665,7 @@
         <v>0</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F144" s="5" t="n">
         <v>0</v>
@@ -23635,7 +23704,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>ZirconiAJP</t>
+          <t>RevenantSA</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
@@ -23687,11 +23756,11 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>DEMIG0DS</t>
+          <t>OBLIxVION</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" s="5" t="n">
         <v>0</v>
@@ -23700,7 +23769,7 @@
         <v>0</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>0</v>
@@ -23718,7 +23787,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" s="5" t="n">
         <v>0</v>
@@ -23739,11 +23808,11 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>ZirconiAJP</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C147" s="5" t="n">
         <v>0</v>
@@ -23776,10 +23845,10 @@
         <v>0</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147" s="5" t="n">
         <v>0</v>
@@ -23791,14 +23860,14 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>PinoyPioneer</t>
+          <t>DEMIG0DS</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>0</v>
@@ -23822,7 +23891,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="5" t="n">
         <v>0</v>
@@ -23843,7 +23912,7 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
@@ -23880,10 +23949,10 @@
         <v>0</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O149" s="5" t="n">
         <v>0</v>
@@ -23895,23 +23964,23 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>죽음LC</t>
+          <t>PinoyPioneer</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5" t="n">
         <v>0</v>
@@ -23947,7 +24016,7 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>知音丶酒吧</t>
+          <t>죽음LC</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -23960,10 +24029,10 @@
         <v>0</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
         <v>0</v>
@@ -23975,10 +24044,10 @@
         <v>0</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="5" t="n">
         <v>0</v>
@@ -23999,11 +24068,11 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Kitanjou</t>
+          <t>知音丶酒吧</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C152" s="5" t="n">
         <v>0</v>
@@ -24027,10 +24096,10 @@
         <v>0</v>
       </c>
       <c r="J152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" s="5" t="n">
         <v>0</v>
@@ -24051,11 +24120,11 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Kitanjou</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C153" s="5" t="n">
         <v>0</v>
@@ -24091,7 +24160,7 @@
         <v>0</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O153" s="5" t="n">
         <v>0</v>
@@ -24103,7 +24172,7 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>彡PAPAROCK彡</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
@@ -24116,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F154" s="5" t="n">
         <v>0</v>
@@ -24143,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O154" s="5" t="n">
         <v>0</v>
@@ -24155,7 +24224,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>彡PAPAROCK彡</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
@@ -24168,7 +24237,7 @@
         <v>0</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F155" s="5" t="n">
         <v>0</v>
@@ -24195,10 +24264,10 @@
         <v>0</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P155" s="5" t="n">
         <v>2</v>
@@ -25631,7 +25700,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -26327,16 +26396,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(43), 雪狼族(40), 沙漠黑鷹(39), 雲淡風輕o(16), 當惡魔遇到殺手貓(14), LeLien(13), ーリベリオンー(11), Unity(9)</t>
+          <t>・殺戮・(44), 雪狼族(41), 沙漠黑鷹(40), 雲淡風輕o(16), 當惡魔遇到殺手貓(15), LeLien(13), ーリベリオンー(11), Unity(9)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(39勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
+          <t>・殺戮・(40勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
         </is>
       </c>
     </row>
@@ -26511,16 +26580,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(38), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(18), TRAITORs(10), Phoenix(8), ・殺戮・(6)</t>
+          <t>AlmaVivaJP(39), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(18), TRAITORs(11), Phoenix(8), ・殺戮・(6)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(27勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
+          <t>AlmaVivaJP(28勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -26623,19 +26692,19 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Unity(17), Maverickz(15), VainqueurJP(11), Phoenix(9), Myst(8), 東京熱株式會社(5), DoraemonSA(5), Döraè่mön(4)</t>
+          <t>Unity(18), Maverickz(15), VainqueurJP(11), Phoenix(9), Myst(8), 東京熱株式會社(5), DoraemonSA(5), Döraè่mön(4)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Unity(14勝), VainqueurJP(10勝), Maverickz(7勝), Myst(6勝), Phoenix(6勝)</t>
+          <t>Unity(15勝), VainqueurJP(10勝), Maverickz(7勝), Myst(6勝), Phoenix(6勝)</t>
         </is>
       </c>
     </row>
@@ -26672,11 +26741,11 @@
         <v>38</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(39), シェイド(22), 一Arch(14), 黒の太陽(11), FLORISTS(10), ーEspoirー(10), xAEGISx(6), ーリベリオンー(5)</t>
+          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(11), 黒の太陽(11), ーEspoirー(10), xAEGISx(6), ーリベリオンー(5)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -26695,16 +26764,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(38), RaиkSS(25), VainqueurJP(25), PONYTAIL(21), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
+          <t>TRAITORs(38), RaиkSS(26), VainqueurJP(26), PONYTAIL(22), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(22勝), RaиkSS(8勝), VainqueurJP(8勝), PONYTAIL(7勝), AlmaVivaJP(5勝)</t>
+          <t>TRAITORs(22勝), RaиkSS(9勝), VainqueurJP(8勝), PONYTAIL(7勝), AlmaVivaJP(5勝)</t>
         </is>
       </c>
     </row>
@@ -26718,16 +26787,16 @@
         <v>40</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(22), Kopitiam(11), ーリベリオンー(8), ZirconiA(7), Иouver(7), 亗Luxúria亗(5), MelonEmpire(5), Orzeca(4)</t>
+          <t>一惡人谷一(22), Kopitiam(11), ーリベリオンー(9), ZirconiA(7), Иouver(7), 柿一門(5), 亗Luxúria亗(5), MelonEmpire(5)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(21勝), ーリベリオンー(7勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
+          <t>一惡人谷一(21勝), ーリベリオンー(8勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
         </is>
       </c>
     </row>
@@ -26830,14 +26899,14 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>一Arch(18), Maverickz(10), TheUniverse(10), 亗Luxúria亗(10), 一SUN一(8), RëBîrth(8), Revenant(7), EIemento(6)</t>
+          <t>一Arch(18), Maverickz(10), TheUniverse(10), 亗Luxúria亗(10), 一SUN一(8), RëBîrth(8), Revenant(7), cobraXverse(6)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -26922,19 +26991,19 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ひよこりあ(27), ーEspoirー(20), 義勇(19), 桜吹雪(19), 月下の集い(18), TheEnd(17), のら猫(14), ZirconiA(13)</t>
+          <t>ひよこりあ(28), ーEspoirー(20), 義勇(19), 桜吹雪(19), 月下の集い(18), TheEnd(17), のら猫(15), ZirconiA(14)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>義勇(10勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(4勝), ーEspoirー(4勝)</t>
+          <t>義勇(10勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝), ーEspoirー(4勝)</t>
         </is>
       </c>
     </row>
@@ -26968,10 +27037,10 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -26980,7 +27049,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(10勝), Restart(9勝), 柿一門(4勝), 一DEFIANCE(3勝), EIemento(2勝)</t>
+          <t>亗Luxúria亗(10勝), Restart(9勝), 柿一門(4勝), 一DEFIANCE(3勝), REGENCY彡(2勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-07</t>
+          <t>2025-08-01 〜 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2118</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3395</v>
+        <v>0.3374</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.3691</v>
+        <v>0.3667</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>31</v>
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1892</v>
+        <v>0.1946</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>41</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2789</v>
+        <v>0.277</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -771,51 +771,51 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.4307</v>
+        <v>0.3478</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>137</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.3504</v>
+        <v>0.4307</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3462</v>
+        <v>0.3435</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.4331</v>
+        <v>0.4297</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>14</v>
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.1102</v>
+        <v>0.1094</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5179</v>
+        <v>0.5133</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5856</v>
+        <v>0.5893</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
@@ -1296,51 +1296,51 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
         <v>98</v>
       </c>
       <c r="C29" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="E29" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0.1531</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.3608</v>
+        <v>0.1531</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.2766</v>
+        <v>0.2737</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>22</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.3407</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.1875</v>
+        <v>0.1852</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>58</v>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1449</v>
+        <v>0.1429</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>51</v>
@@ -1646,51 +1646,51 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
         <v>68</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.7206</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.7164</v>
+        <v>0.1471</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1700,19 +1700,19 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.6818</v>
+        <v>0.6716</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>2</v>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1587</v>
+        <v>0.1562</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>5</v>
@@ -1871,23 +1871,23 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.2</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0</v>
@@ -1896,23 +1896,23 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.2222</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
@@ -1921,23 +1921,23 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.2037</v>
+        <v>0.1111</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -2121,73 +2121,73 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0.4118</v>
+        <v>0.2571</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>一DEFIANCE</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>0.3529</v>
+        <v>0.4118</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.2647</v>
+        <v>0.1471</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0</v>
@@ -2196,76 +2196,76 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>一DEFIANCE</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>0.1176</v>
+        <v>0.3529</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>13</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>0.2059</v>
+        <v>0.1176</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>0.1515</v>
+        <v>0.2059</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2275,16 +2275,16 @@
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>0.4062</v>
+        <v>0.4242</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>26</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>12</v>
@@ -2521,23 +2521,23 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>SanctaTerra</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
         <v>22</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.2727</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G78" s="5" t="n">
         <v>0</v>
@@ -2546,23 +2546,23 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>SanctaTerra</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>0.2381</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>0</v>
@@ -3496,23 +3496,23 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
@@ -3521,23 +3521,23 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -3559,7 +3559,7 @@
         <v>0.1667</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>16</v>
@@ -3571,23 +3571,23 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3596,23 +3596,23 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>0.6</v>
+        <v>0.1667</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>0</v>
@@ -3621,23 +3621,23 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G122" s="5" t="n">
         <v>0</v>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>21</v>
@@ -5589,40 +5589,40 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>2</v>
@@ -5631,91 +5631,91 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -5724,40 +5724,40 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -5769,10 +5769,10 @@
         <v>23</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5820,106 +5820,106 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -5930,17 +5930,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -6114,19 +6114,19 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>7</v>
@@ -6135,28 +6135,28 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -6165,136 +6165,136 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>4</v>
@@ -6345,40 +6345,40 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D58" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D58" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E58" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>5</v>
@@ -6387,61 +6387,61 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>4</v>
@@ -6450,127 +6450,127 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -6581,182 +6581,182 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>6</v>
@@ -6765,22 +6765,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -7857,12 +7857,12 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
@@ -7872,18 +7872,18 @@
         <v>3</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
@@ -7893,18 +7893,18 @@
         <v>2</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
@@ -7914,46 +7914,46 @@
         <v>3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" s="5" t="n">
         <v>4</v>
@@ -7962,37 +7962,37 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>2</v>
@@ -8004,33 +8004,33 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
@@ -8040,67 +8040,67 @@
         <v>2</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
           <t>義勇</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5" t="n">
         <v>3</v>
@@ -8109,28 +8109,28 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -8142,21 +8142,21 @@
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
@@ -8172,64 +8172,64 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -8240,14 +8240,14 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E148" s="5" t="n">
         <v>3</v>
@@ -8256,138 +8256,138 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
@@ -8397,214 +8397,214 @@
         <v>4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="5" t="n">
         <v>3</v>
@@ -8613,40 +8613,40 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E167" s="5" t="n">
         <v>4</v>
@@ -8655,12 +8655,12 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
@@ -8670,25 +8670,25 @@
         <v>1</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5" t="n">
         <v>1</v>
@@ -8697,7 +8697,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -8709,7 +8709,7 @@
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>1</v>
@@ -8718,28 +8718,28 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -8751,10 +8751,10 @@
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
@@ -8775,13 +8775,13 @@
         <v>3</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -8793,7 +8793,7 @@
         <v>10</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E174" s="5" t="n">
         <v>0</v>
@@ -8802,75 +8802,75 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
@@ -8880,67 +8880,67 @@
         <v>2</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E181" s="5" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -8970,22 +8970,22 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -9377,7 +9377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9464,26 +9464,26 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
@@ -9493,12 +9493,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
@@ -10885,26 +10885,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
@@ -10914,55 +10914,55 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D53" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="E53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
           <t>ーEspoirー</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>柿一門</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
@@ -11146,26 +11146,26 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -11175,12 +11175,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
@@ -11204,55 +11204,55 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
@@ -11262,55 +11262,55 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0.846</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G66" s="6" t="n">
@@ -11320,7 +11320,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -11349,12 +11349,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
@@ -11378,7 +11378,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -11407,12 +11407,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11436,26 +11436,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
@@ -11465,84 +11465,84 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.833</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -11552,12 +11552,12 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11581,26 +11581,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -11610,26 +11610,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
@@ -11639,7 +11639,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -11668,12 +11668,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
@@ -11697,12 +11697,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
@@ -11726,26 +11726,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11755,26 +11755,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11784,26 +11784,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11813,12 +11813,12 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11842,26 +11842,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E85" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11871,26 +11871,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11900,12 +11900,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11929,26 +11929,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11958,26 +11958,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -11987,26 +11987,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12016,58 +12016,29 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G91" s="6" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Maverickz</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12132,7 +12103,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0827</v>
       </c>
     </row>
     <row r="3">
@@ -12145,10 +12116,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2035</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="4">
@@ -12161,10 +12132,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4174</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="5">
@@ -12177,10 +12148,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0793</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="6">
@@ -12193,10 +12164,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2167</v>
+        <v>0.2163</v>
       </c>
     </row>
   </sheetData>
@@ -12210,7 +12181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12314,11 +12285,11 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:6勝, 一SUN一:4勝</t>
+          <t>Orzeca:7勝, 一SUN一:4勝</t>
         </is>
       </c>
     </row>
@@ -13460,7 +13431,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、TRAITORs</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -13468,7 +13439,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13454,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PokemonGo</t>
+          <t>Maverickz、TRAITORs</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -13491,7 +13462,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13477,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs</t>
+          <t>Maverickz、PokemonGo</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -13514,7 +13485,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13500,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse</t>
+          <t>PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -13537,7 +13508,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -13552,7 +13523,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Döraè่mön</t>
+          <t>Döraè่mön、cobraXverse</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -13560,7 +13531,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13546,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、雲淡風輕o</t>
+          <t>AlmaVivaJP、Döraè่mön</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -13583,7 +13554,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13569,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、心晴</t>
+          <t>VainqueurJP、雲淡風輕o</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -13606,7 +13577,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13592,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Kaioken、TipsyTavern</t>
+          <t>PokemonGo、心晴</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -13629,7 +13600,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>TipsyTavern:1勝, Kaioken:1勝</t>
+          <t>PokemonGo:2勝</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13615,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、一惡人谷一</t>
+          <t>Kaioken、TipsyTavern</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
@@ -13652,7 +13623,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
+          <t>TipsyTavern:1勝, Kaioken:1勝</t>
         </is>
       </c>
     </row>
@@ -13667,7 +13638,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、毛家村</t>
+          <t>Maverickz、一惡人谷一</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -13675,7 +13646,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>毛家村:2勝</t>
+          <t>一惡人谷一:2勝</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13661,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>一DEFIANCE、雲淡風輕o</t>
+          <t>Etërnîty、一惡人谷一</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
@@ -13698,7 +13669,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:2勝</t>
+          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13684,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>MÏRÃGË、雲淡風輕o</t>
+          <t>CatlandTHM、毛家村</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -13721,7 +13692,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
+          <t>毛家村:2勝</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13707,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、雲淡風輕o</t>
+          <t>一DEFIANCE、雲淡風輕o</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -13759,7 +13730,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、美孚冰室</t>
+          <t>MÏRÃGË、雲淡風輕o</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -13767,7 +13738,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝</t>
+          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13753,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、溫柔鄉</t>
+          <t>CatlandTHM、雲淡風輕o</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
@@ -13790,7 +13761,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
+          <t>雲淡風輕o:2勝</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13776,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PONYTAIL</t>
+          <t>Döraè่mön、美孚冰室</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -13813,53 +13784,53 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>微笑Party、溫柔鄉</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
+          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
+          <t>Maverickz、PONYTAIL</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13874,15 +13845,15 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
+          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:5勝, Kopitiam:5勝, MelonEmpire:4勝</t>
+          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
         </is>
       </c>
     </row>
@@ -13897,15 +13868,15 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、TRAITORs</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
+          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
         </is>
       </c>
     </row>
@@ -13920,15 +13891,15 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
+          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
+          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:4勝</t>
         </is>
       </c>
     </row>
@@ -13943,15 +13914,15 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>PONYTAIL、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -13966,15 +13937,15 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13989,15 +13960,15 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -14012,15 +13983,15 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝, VainqueurJP:2勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -14035,15 +14006,15 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -14058,15 +14029,15 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14081,7 +14052,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -14089,7 +14060,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14075,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14112,7 +14083,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14098,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -14135,7 +14106,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14121,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14158,7 +14129,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14144,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14181,7 +14152,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14167,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、PONYTAIL</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14204,7 +14175,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝</t>
+          <t>RaиkSS:4勝</t>
         </is>
       </c>
     </row>
@@ -14219,7 +14190,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14227,7 +14198,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14213,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、PONYTAIL</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14250,7 +14221,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>AlmaVivaJP:4勝</t>
         </is>
       </c>
     </row>
@@ -14265,15 +14236,15 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14288,15 +14259,15 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14282,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -14319,7 +14290,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14305,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
@@ -14342,7 +14313,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14328,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -14365,7 +14336,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14351,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14388,7 +14359,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14374,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14411,7 +14382,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14397,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14434,7 +14405,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14420,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14457,7 +14428,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14472,15 +14443,15 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14495,15 +14466,15 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14489,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14526,7 +14497,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14512,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14549,7 +14520,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14535,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14572,7 +14543,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14558,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14595,7 +14566,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14581,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14618,7 +14589,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14604,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14641,7 +14612,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14656,7 +14627,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14664,7 +14635,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14650,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14687,7 +14658,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14673,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14710,7 +14681,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14696,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14733,7 +14704,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14719,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14756,7 +14727,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14742,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14779,7 +14750,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14765,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14817,7 +14788,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14825,7 +14796,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14811,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14848,7 +14819,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14834,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14871,7 +14842,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14886,7 +14857,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14894,7 +14865,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14880,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14917,7 +14888,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14903,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14940,7 +14911,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14926,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14963,7 +14934,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14949,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -14986,7 +14957,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15001,7 +14972,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15009,7 +14980,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15024,7 +14995,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15032,7 +15003,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15018,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15055,7 +15026,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15041,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15078,7 +15049,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15064,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15101,7 +15072,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15087,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15124,7 +15095,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15110,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15147,7 +15118,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15162,7 +15133,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15185,7 +15156,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15193,7 +15164,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15179,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15216,7 +15187,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15202,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15239,7 +15210,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15225,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15262,7 +15233,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15248,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15285,7 +15256,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15271,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15308,7 +15279,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15294,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15331,7 +15302,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15317,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15354,7 +15325,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15340,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15377,7 +15348,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15363,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15400,7 +15371,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15386,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15423,7 +15394,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15409,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15446,7 +15417,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15432,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15469,7 +15440,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15455,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15492,7 +15463,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15478,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15515,7 +15486,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15501,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15538,7 +15509,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15524,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15561,7 +15532,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15576,7 +15547,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15584,7 +15555,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15570,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15607,7 +15578,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15593,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15630,7 +15601,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15616,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15653,53 +15624,53 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15714,15 +15685,15 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15737,15 +15708,15 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15760,15 +15731,15 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15754,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -15791,7 +15762,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15777,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15814,7 +15785,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15800,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15837,7 +15808,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15823,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15860,7 +15831,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15846,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -15883,7 +15854,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15869,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15906,7 +15877,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15892,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15929,45 +15900,45 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:4勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -15975,22 +15946,22 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -15998,7 +15969,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16013,15 +15984,15 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:4勝</t>
         </is>
       </c>
     </row>
@@ -16036,7 +16007,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -16059,7 +16030,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16067,7 +16038,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16053,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16090,7 +16061,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16076,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16113,7 +16084,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16099,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16136,7 +16107,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16122,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -16159,7 +16130,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16145,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16182,7 +16153,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16197,13 +16168,82 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D173" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="D176" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16369,10 +16409,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
@@ -16473,10 +16513,10 @@
         <v>13</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -16525,10 +16565,10 @@
         <v>16</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6">
@@ -16577,10 +16617,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
@@ -16638,102 +16678,102 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="N8" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="I9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="O9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>137</v>
@@ -16785,10 +16825,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -16837,10 +16877,10 @@
         <v>10</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -16889,10 +16929,10 @@
         <v>8</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -17253,10 +17293,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
@@ -17305,10 +17345,10 @@
         <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21">
@@ -17730,50 +17770,50 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>98</v>
@@ -17782,53 +17822,53 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="L30" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
@@ -17929,10 +17969,10 @@
         <v>9</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33">
@@ -17981,10 +18021,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
@@ -18137,10 +18177,10 @@
         <v>16</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
@@ -18449,59 +18489,59 @@
         <v>9</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43" s="5" t="n">
         <v>68</v>
@@ -18510,53 +18550,53 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="H44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="K44" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45">
@@ -18605,10 +18645,10 @@
         <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46">
@@ -18709,10 +18749,10 @@
         <v>10</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
@@ -18926,102 +18966,102 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O52" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P52" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="L53" s="5" t="n">
         <v>3</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="5" t="n">
         <v>54</v>
@@ -19030,7 +19070,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -19040,40 +19080,40 @@
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I54" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="J54" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="L54" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P54" s="5" t="n">
         <v>54</v>
@@ -19446,99 +19486,99 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C62" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D62" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="N62" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>一DEFIANCE</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="5" t="n">
         <v>0</v>
@@ -19550,50 +19590,50 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C64" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D64" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P64" s="5" t="n">
         <v>34</v>
@@ -19602,38 +19642,38 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>一DEFIANCE</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>4</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L65" s="5" t="n">
         <v>0</v>
@@ -19642,7 +19682,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="5" t="n">
         <v>0</v>
@@ -19654,38 +19694,38 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
@@ -19694,7 +19734,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="5" t="n">
         <v>0</v>
@@ -19706,44 +19746,44 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" s="5" t="n">
         <v>0</v>
@@ -19752,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68">
@@ -19801,10 +19841,10 @@
         <v>11</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69">
@@ -20217,10 +20257,10 @@
         <v>1</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -20278,11 +20318,11 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>SanctaTerra</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C78" s="5" t="n">
         <v>0</v>
@@ -20291,19 +20331,19 @@
         <v>0</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>0</v>
@@ -20312,16 +20352,16 @@
         <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P78" s="5" t="n">
         <v>22</v>
@@ -20330,11 +20370,11 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>SanctaTerra</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>0</v>
@@ -20343,19 +20383,19 @@
         <v>0</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" s="5" t="n">
         <v>0</v>
@@ -20364,19 +20404,19 @@
         <v>0</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -22306,7 +22346,7 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -22331,25 +22371,25 @@
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P117" s="5" t="n">
         <v>6</v>
@@ -22358,17 +22398,17 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>0</v>
@@ -22383,16 +22423,16 @@
         <v>0</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M118" s="5" t="n">
         <v>0</v>
@@ -22401,7 +22441,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" s="5" t="n">
         <v>6</v>
@@ -22410,17 +22450,17 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
         <v>0</v>
@@ -22462,7 +22502,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -22472,25 +22512,25 @@
         <v>0</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" s="5" t="n">
         <v>0</v>
@@ -22502,10 +22542,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P120" s="5" t="n">
         <v>6</v>
@@ -22514,14 +22554,14 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" s="5" t="n">
         <v>0</v>
@@ -22554,19 +22594,19 @@
         <v>0</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P121" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -22576,25 +22616,25 @@
         <v>0</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" s="5" t="n">
         <v>0</v>
@@ -22606,13 +22646,13 @@
         <v>0</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -25740,7 +25780,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -25758,7 +25798,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -25800,7 +25840,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25818,7 +25858,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25830,7 +25870,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -25848,7 +25888,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -26467,16 +26507,16 @@
         <v>51</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ーEspoirー(18), Revenant(16), SanctaTerra(15), C0BRA(15), 厶pocalypse(14), EIemento(13), Bagaиเ่(13), 柿一門(12)</t>
+          <t>ーEspoirー(19), Revenant(17), 厶pocalypse(15), SanctaTerra(15), C0BRA(15), 柿一門(13), EIemento(13), Bagaиเ่(13)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(8勝), Restart(7勝), ーEspoirー(6勝), 柿一門(5勝), Revenant(5勝)</t>
+          <t>亗Luxúria亗(8勝), Restart(7勝), 柿一門(6勝), ーEspoirー(6勝), Revenant(5勝)</t>
         </is>
       </c>
     </row>
@@ -26579,10 +26619,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -26717,14 +26757,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>一Arch(13), PokemonGo(12), Maverickz(7), Döraè่mön(7), FLORISTS(6), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
+          <t>一Arch(13), PokemonGo(12), FLORISTS(7), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -26766,16 +26806,16 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Unity(29), 黒の太陽(20), シェイド(19), xAEGISx(15), ーリベリオンー(12), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
+          <t>Unity(30), 黒の太陽(21), シェイド(19), xAEGISx(16), ーリベリオンー(13), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽(7勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
+          <t>黒の太陽(8勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
         </is>
       </c>
     </row>
@@ -26904,16 +26944,16 @@
         <v>34</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(31), ßบรнíïdо丶ๅ家族(26), Kopitiam(25), MelonEmpire(9), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
+          <t>亗Luxúria亗(32), Kopitiam(26), ßบรнíïdо丶ๅ家族(26), MelonEmpire(10), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam(23勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
+          <t>Kopitiam(24勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
         </is>
       </c>
     </row>
@@ -26970,10 +27010,10 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -27019,16 +27059,16 @@
         <v>28</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(19), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
+          <t>一惡人谷一(20), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(15勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
+          <t>一惡人谷一(16勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
         </is>
       </c>
     </row>
@@ -27065,16 +27105,16 @@
         <v>35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(27), RaиkSS(20), 雲淡風輕o(17), 當惡魔遇到殺手貓(16), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
+          <t>PONYTAIL(28), RaиkSS(20), 當惡魔遇到殺手貓(17), 雲淡風輕o(17), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(24勝), RaиkSS(16勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
+          <t>PONYTAIL(25勝), RaиkSS(16勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27249,11 +27289,11 @@
         <v>51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>柿一門(28), 義勇(21), 桜吹雪(18), 黄昏のえりしおん(16), ひよこりあ(16), Pandora(15), Restart(14), 氣噗噗讓玻璃心碎一地(11)</t>
+          <t>柿一門(28), 義勇(21), 桜吹雪(18), 黄昏のえりしおん(16), ひよこりあ(16), Pandora(15), Restart(14), 氣噗噗讓玻璃心碎一地(12)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
